--- a/Apostas_Diarias/Apostas_20260414.xlsx
+++ b/Apostas_Diarias/Apostas_20260414.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_2B590F4F954644AFD0025D70571510344D07F755" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2003791-33CF-49E9-B740-884DEB8A6626}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_2B590F4F951647206ABC76535D1510344D07F140" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{936AFCF3-C3FE-4C9E-8269-13D164665586}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Data</t>
   </si>
@@ -74,22 +74,16 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
-    <t>BULGARIA 1</t>
-  </si>
-  <si>
-    <t>Botev Vratsa x Lokomotiv Sofia</t>
+    <t>10:15:00</t>
+  </si>
+  <si>
+    <t>SAUDI ARABIA 1</t>
+  </si>
+  <si>
+    <t>Al-Jndal x Al-Ula FC</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
-  </si>
-  <si>
-    <t>14:30:00</t>
-  </si>
-  <si>
-    <t>Dobrudzha x Botev Plovdiv</t>
   </si>
 </sst>
 </file>
@@ -429,14 +423,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -479,9 +473,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -503,14 +494,12 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>9.1999999999999993</v>
+        <v>9.4</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>9.1999999999999993</v>
+        <v>9.4</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -519,51 +508,9 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>57.01219512195123</v>
+        <v>55.654761904761905</v>
       </c>
       <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="H3">
-        <f>G3</f>
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="I3">
-        <f>$L$1</f>
-        <v>500</v>
-      </c>
-      <c r="J3" t="str">
-        <f>IF(L3=1,"GREEN","RED")</f>
-        <v>GREEN</v>
-      </c>
-      <c r="K3">
-        <f>IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>53.125</v>
-      </c>
-      <c r="L3">
         <v>1</v>
       </c>
     </row>
